--- a/rover_platform_mbse/export/ROVER-A1-ROVER_CONTROLLER-SWRS-V-001.xlsx
+++ b/rover_platform_mbse/export/ROVER-A1-ROVER_CONTROLLER-SWRS-V-001.xlsx
@@ -1972,7 +1972,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-07</t>
         </is>
       </c>
     </row>
@@ -2086,7 +2086,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">

--- a/rover_platform_mbse/export/ROVER-A1-ROVER_CONTROLLER-SWRS-V-001.xlsx
+++ b/rover_platform_mbse/export/ROVER-A1-ROVER_CONTROLLER-SWRS-V-001.xlsx
@@ -838,12 +838,12 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>The rover_controller shall configure rover_drive_controller with wheel_separation 0.615 m, wheel_radius 0.1651 m, wheels_per_side 2, wheel_separation_multiplier 1.659, left/right wheel_radius_multiplier 1.0 and update_rate 50 Hz.</t>
+          <t>The rover_controller shall configure rover_drive_controller with wheel_separation 0.617 m, wheel_radius 0.1651 m, wheels_per_side 2, wheel_separation_multiplier 1.659, left/right wheel_radius_multiplier 1.0 and update_rate 50 Hz.</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>SYS-SR-003 skid-steer kinematics. The separation multiplier is the empirical skid-steer correction (effective track 0.615 x 1.659 = 1.020 m), not geometry.</t>
+          <t>SYS-SR-003 skid-steer kinematics. The separation multiplier is the empirical skid-steer correction (effective track 0.617 x 1.659 = 1.0236 m), not geometry.</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>rover_controller/config/wheel_01_controller.yaml:157-178</t>
+          <t>rover_controller/config/wheel_01_controller.yaml:242-252</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t>Doc drift: rover_description/README.md:79 still cites wheel_separation_multiplier 1.5. The multiplier was rescaled from a 1.63 calibration against the old 0.62602 m separation (yaml:173-174), not re-measured.</t>
+          <t>The multiplier 1.659 was rescaled from a 1.63 calibration against the old 0.62602 m separation to a measured 0.615 m (yaml:247-248). wheel_separation was later set to the CAD wheel-joint distance 0.617 m without rescaling it, so the effective track is 1.0236 m against the calibrated 1.020 m and rover_crsf_teleop effective_track_width 1.0204 m (docs/open-items.md, Source conflicts). The tyre contact patches are 0.6136 m apart (the tread sits 1.71 mm inboard of each wheel joint; rover_description wheel_01.yaml tyre_y_offset).</t>
         </is>
       </c>
     </row>

--- a/rover_platform_mbse/export/ROVER-A1-ROVER_CONTROLLER-SWRS-V-001.xlsx
+++ b/rover_platform_mbse/export/ROVER-A1-ROVER_CONTROLLER-SWRS-V-001.xlsx
@@ -1972,7 +1972,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
     </row>
@@ -2086,7 +2086,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
